--- a/12626052.xlsx
+++ b/12626052.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E56BF78-29AD-4048-A28F-D378D9B5978E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF2BAD7A-7DA6-478C-A185-192B5C34EC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,6 +202,18 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>SHIVNATH KUMAR</t>
+  </si>
+  <si>
+    <t>CAP776/D1P2636</t>
+  </si>
+  <si>
+    <t>AUGEST</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
@@ -888,26 +900,34 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12626052</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>57</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1198,368 +1218,710 @@
       <c r="A11" s="13">
         <v>46249</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>35</v>
+      </c>
+      <c r="D11" s="14">
+        <v>130</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>350</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>505</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>46250</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="B12" s="14">
+        <v>350</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>130</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46251</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="B13" s="14">
+        <v>350</v>
+      </c>
+      <c r="C13" s="14">
+        <v>35</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>835</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>605</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46252</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>130</v>
+      </c>
+      <c r="E14" s="14">
+        <v>40</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>46253</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>40</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>46254</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="B16" s="14">
+        <v>400</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>130</v>
+      </c>
+      <c r="E16" s="14">
+        <v>40</v>
+      </c>
+      <c r="F16" s="14">
+        <v>350</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>130</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>350</v>
+      </c>
+      <c r="G17" s="14">
+        <v>7</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="14">
+        <v>350</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B19" s="14">
+        <v>350</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>130</v>
+      </c>
+      <c r="E19" s="14">
+        <v>30</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B21" s="14">
+        <v>350</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>130</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="14">
+        <v>350</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>300</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>130</v>
+      </c>
+      <c r="E24" s="14">
+        <v>40</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>350</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>350</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>350</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>123</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>883</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>557</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
+      <c r="A27" s="13">
+        <v>46265</v>
+      </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -1581,7 +1943,9 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
+      <c r="A28" s="13">
+        <v>46266</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -1603,7 +1967,9 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
+      <c r="A29" s="13">
+        <v>46267</v>
+      </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -1625,7 +1991,9 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13">
+        <v>46268</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -1647,7 +2015,9 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
+      <c r="A31" s="13">
+        <v>46269</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -1669,7 +2039,9 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
+      <c r="A32" s="13">
+        <v>46270</v>
+      </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -1691,7 +2063,9 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13">
+        <v>46271</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
@@ -1713,7 +2087,9 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
+      <c r="A34" s="13">
+        <v>46272</v>
+      </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
@@ -1735,7 +2111,9 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
@@ -1757,7 +2135,9 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -1779,7 +2159,9 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13">
+        <v>46275</v>
+      </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -1801,7 +2183,9 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -1823,7 +2207,9 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13">
+        <v>46277</v>
+      </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -1845,7 +2231,9 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
+      <c r="A40" s="13">
+        <v>46278</v>
+      </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -1867,7 +2255,9 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
+      <c r="A41" s="13">
+        <v>46279</v>
+      </c>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -1889,7 +2279,9 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
+      <c r="A42" s="13">
+        <v>46280</v>
+      </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -1911,7 +2303,9 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
+      <c r="A43" s="13">
+        <v>46281</v>
+      </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -1933,7 +2327,9 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
+      <c r="A44" s="13">
+        <v>46282</v>
+      </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -1955,7 +2351,9 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
+      <c r="A45" s="13">
+        <v>46283</v>
+      </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -1977,7 +2375,9 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
+      <c r="A46" s="13">
+        <v>46284</v>
+      </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>

--- a/12626052.xlsx
+++ b/12626052.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF2BAD7A-7DA6-478C-A185-192B5C34EC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCA0B91F-F205-407B-9CA6-CB2585A02EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1099,21 +1105,21 @@
         <v>40</v>
       </c>
       <c r="F8" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G8" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H8" s="14">
         <v>40</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>870</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>49</v>
@@ -1143,21 +1149,21 @@
         <v>0</v>
       </c>
       <c r="F9" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G9" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" s="14">
         <v>0</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>770</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>670</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>49</v>
@@ -1187,21 +1193,21 @@
         <v>0</v>
       </c>
       <c r="F10" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G10" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" s="14">
         <v>0</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>630</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1231,21 +1237,21 @@
         <v>0</v>
       </c>
       <c r="F11" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
         <v>0</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>935</v>
+        <v>585</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>505</v>
+        <v>855</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>49</v>
@@ -1275,21 +1281,21 @@
         <v>0</v>
       </c>
       <c r="F12" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14">
         <v>0</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>510</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>930</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1319,21 +1325,21 @@
         <v>30</v>
       </c>
       <c r="F13" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G13" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" s="14">
         <v>0</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>835</v>
+        <v>785</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>605</v>
+        <v>655</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1451,21 +1457,21 @@
         <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>640</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>49</v>
@@ -1495,21 +1501,21 @@
         <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G17" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
         <v>0</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1539,21 +1545,21 @@
         <v>30</v>
       </c>
       <c r="F18" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H18" s="14">
         <v>0</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>530</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>910</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>49</v>
@@ -1583,21 +1589,21 @@
         <v>30</v>
       </c>
       <c r="F19" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14">
         <v>0</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>540</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>900</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>49</v>
@@ -1627,21 +1633,21 @@
         <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
         <v>0</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>730</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1671,21 +1677,21 @@
         <v>30</v>
       </c>
       <c r="F21" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G21" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="14">
         <v>0</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>880</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>560</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>49</v>
@@ -1715,21 +1721,21 @@
         <v>30</v>
       </c>
       <c r="F22" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14">
         <v>0</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>780</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>660</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>49</v>
@@ -1759,21 +1765,21 @@
         <v>30</v>
       </c>
       <c r="F23" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
         <v>0</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>730</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>710</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1803,21 +1809,21 @@
         <v>40</v>
       </c>
       <c r="F24" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G24" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H24" s="14">
         <v>0</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>740</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
@@ -1847,21 +1853,21 @@
         <v>30</v>
       </c>
       <c r="F25" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14">
         <v>0</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>530</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>910</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -1891,21 +1897,21 @@
         <v>30</v>
       </c>
       <c r="F26" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G26" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H26" s="14">
         <v>0</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>883</v>
+        <v>533</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>557</v>
+        <v>907</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -1922,264 +1928,484 @@
       <c r="A27" s="13">
         <v>46265</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="B27" s="14">
+        <v>350</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <v>46266</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="B28" s="14">
+        <v>300</v>
+      </c>
+      <c r="C28" s="14">
+        <v>35</v>
+      </c>
+      <c r="D28" s="14">
+        <v>130</v>
+      </c>
+      <c r="E28" s="14">
+        <v>40</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>30</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>555</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
         <v>46267</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="B29" s="14">
+        <v>350</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>140</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>20</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>46268</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="B30" s="14">
+        <v>350</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>40</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
         <v>46269</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="B31" s="14">
+        <v>300</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>130</v>
+      </c>
+      <c r="E31" s="14">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>30</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
         <v>46270</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="B32" s="14">
+        <v>350</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>40</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>40</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>860</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
         <v>46271</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>40</v>
+      </c>
+      <c r="D33" s="14">
+        <v>130</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>40</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
         <v>46272</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="B34" s="14">
+        <v>350</v>
+      </c>
+      <c r="C34" s="14">
+        <v>40</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>40</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>40</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
         <v>46273</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="B35" s="14">
+        <v>350</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>130</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>30</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>46274</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="B36" s="14">
+        <v>300</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>40</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>40</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
         <v>46275</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="B37" s="14">
+        <v>350</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>130</v>
+      </c>
+      <c r="E37" s="14">
+        <v>40</v>
+      </c>
+      <c r="F37" s="14">
+        <v>200</v>
+      </c>
+      <c r="G37" s="14">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14">
+        <v>30</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">

--- a/12626052.xlsx
+++ b/12626052.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCA0B91F-F205-407B-9CA6-CB2585A02EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8357E4FE-D94B-4A80-B157-EA976D590816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -2412,120 +2418,220 @@
       <c r="A38" s="13">
         <v>46276</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="B38" s="14">
+        <v>350</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>20</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
         <v>46277</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="B39" s="14">
+        <v>350</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>130</v>
+      </c>
+      <c r="E39" s="14">
+        <v>50</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>760</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
         <v>46278</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="B40" s="14">
+        <v>350</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>120</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>820</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13">
         <v>46279</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="B41" s="14">
+        <v>350</v>
+      </c>
+      <c r="C41" s="14">
+        <v>40</v>
+      </c>
+      <c r="D41" s="14">
+        <v>130</v>
+      </c>
+      <c r="E41" s="14">
+        <v>30</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>30</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
         <v>46280</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="B42" s="14">
+        <v>350</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>40</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>30</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">

--- a/12626052.xlsx
+++ b/12626052.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8357E4FE-D94B-4A80-B157-EA976D590816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D637A2C1-63A4-410A-908B-606DD0FC9921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2638,96 +2638,176 @@
       <c r="A43" s="13">
         <v>46281</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="B43" s="14">
+        <v>300</v>
+      </c>
+      <c r="C43" s="14">
+        <v>30</v>
+      </c>
+      <c r="D43" s="14">
+        <v>130</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>30</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>46282</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="B44" s="14">
+        <v>350</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>40</v>
+      </c>
+      <c r="F44" s="14">
+        <v>200</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>40</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13">
         <v>46283</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="B45" s="14">
+        <v>350</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>130</v>
+      </c>
+      <c r="E45" s="14">
+        <v>30</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>40</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13">
         <v>46284</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="B46" s="14">
+        <v>360</v>
+      </c>
+      <c r="C46" s="14">
+        <v>40</v>
+      </c>
+      <c r="D46" s="14">
+        <v>60</v>
+      </c>
+      <c r="E46" s="14">
+        <v>50</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>120</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>810</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">

--- a/12626052.xlsx
+++ b/12626052.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D637A2C1-63A4-410A-908B-606DD0FC9921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B7508C-2309-4F4B-99B5-8D416DEA845F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2811,73 +2811,141 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B47" s="14">
+        <v>350</v>
+      </c>
+      <c r="C47" s="14">
+        <v>40</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>150</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="14">
+        <v>350</v>
+      </c>
+      <c r="C48" s="14">
+        <v>40</v>
+      </c>
+      <c r="D48" s="14">
+        <v>120</v>
+      </c>
+      <c r="E48" s="14">
+        <v>40</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>40</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="14">
+        <v>350</v>
+      </c>
+      <c r="C49" s="14">
+        <v>40</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>40</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>30</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
+      <c r="A50" s="13">
+        <v>46288</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>

--- a/12626052.xlsx
+++ b/12626052.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B7508C-2309-4F4B-99B5-8D416DEA845F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{422EF849-5E5C-4B54-B52E-D4A30AD78D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2946,68 +2946,132 @@
       <c r="A50" s="13">
         <v>46288</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="B50" s="14">
+        <v>350</v>
+      </c>
+      <c r="C50" s="14">
+        <v>40</v>
+      </c>
+      <c r="D50" s="14">
+        <v>120</v>
+      </c>
+      <c r="E50" s="14">
+        <v>40</v>
+      </c>
+      <c r="F50" s="14">
+        <v>350</v>
+      </c>
+      <c r="G50" s="14">
+        <v>7</v>
+      </c>
+      <c r="H50" s="14">
+        <v>30</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B51" s="14">
+        <v>300</v>
+      </c>
+      <c r="C51" s="14">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>120</v>
+      </c>
+      <c r="E51" s="14">
+        <v>40</v>
+      </c>
+      <c r="F51" s="14">
+        <v>300</v>
+      </c>
+      <c r="G51" s="14">
+        <v>6</v>
+      </c>
+      <c r="H51" s="14">
+        <v>30</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B52" s="14">
+        <v>300</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>120</v>
+      </c>
+      <c r="E52" s="14">
+        <v>40</v>
+      </c>
+      <c r="F52" s="14">
+        <v>350</v>
+      </c>
+      <c r="G52" s="14">
+        <v>7</v>
+      </c>
+      <c r="H52" s="14">
+        <v>30</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">

--- a/12626052.xlsx
+++ b/12626052.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{422EF849-5E5C-4B54-B52E-D4A30AD78D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E926FFE-551D-40AC-8BFB-9FA35283995B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3075,51 +3075,97 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B53" s="14">
+        <v>300</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>120</v>
+      </c>
+      <c r="E53" s="14">
+        <v>40</v>
+      </c>
+      <c r="F53" s="14">
+        <v>300</v>
+      </c>
+      <c r="G53" s="14">
+        <v>6</v>
+      </c>
+      <c r="H53" s="14">
+        <v>30</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B54" s="14">
+        <v>300</v>
+      </c>
+      <c r="C54" s="14">
+        <v>30</v>
+      </c>
+      <c r="D54" s="14">
+        <v>120</v>
+      </c>
+      <c r="E54" s="14">
+        <v>40</v>
+      </c>
+      <c r="F54" s="14">
+        <v>300</v>
+      </c>
+      <c r="G54" s="14">
+        <v>6</v>
+      </c>
+      <c r="H54" s="14">
+        <v>30</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
+      <c r="A55" s="13">
+        <v>46293</v>
+      </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -3141,7 +3187,9 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
+      <c r="A56" s="13">
+        <v>46294</v>
+      </c>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -3163,7 +3211,9 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
+      <c r="A57" s="13">
+        <v>46295</v>
+      </c>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -3185,7 +3235,9 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
+      <c r="A58" s="13">
+        <v>46296</v>
+      </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
@@ -3207,7 +3259,9 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
+      <c r="A59" s="13">
+        <v>46297</v>
+      </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -3229,7 +3283,9 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
+      <c r="A60" s="13">
+        <v>46298</v>
+      </c>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -3251,7 +3307,9 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
+      <c r="A61" s="13">
+        <v>46299</v>
+      </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
@@ -3273,7 +3331,9 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
+      <c r="A62" s="13">
+        <v>46300</v>
+      </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
@@ -3295,7 +3355,9 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
+      <c r="A63" s="13">
+        <v>46301</v>
+      </c>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3317,7 +3379,9 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
+      <c r="A64" s="13">
+        <v>46302</v>
+      </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3339,7 +3403,9 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
+      <c r="A65" s="13">
+        <v>46303</v>
+      </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3361,7 +3427,9 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+      <c r="A66" s="13">
+        <v>46304</v>
+      </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3383,7 +3451,9 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
+      <c r="A67" s="13">
+        <v>46305</v>
+      </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3405,7 +3475,9 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
+      <c r="A68" s="13">
+        <v>46306</v>
+      </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3427,7 +3499,9 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
+      <c r="A69" s="13">
+        <v>46307</v>
+      </c>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
